--- a/clase_s1/datasets_powerbi_parcial/03_rendimiento_academico_powerbi.xlsx
+++ b/clase_s1/datasets_powerbi_parcial/03_rendimiento_academico_powerbi.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="1" r:id="R42a184e232fe41b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estudiantes" sheetId="2" r:id="R13fe6051c72f448a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cursos" sheetId="3" r:id="Ree77105e5a1b4c8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="1" r:id="R0b971098a3bf4c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estudiantes" sheetId="2" r:id="R6e6a85b46a7a4480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cursos" sheetId="3" r:id="Rd3e3032784c34101"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1032,7 +1032,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb788371d989c4308"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04ad3ee2af184d40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1176,7 +1176,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d092df08e254e20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a04afce7fc34940"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1264,7 +1264,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb9ff147bb154f03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac6190e54a56457f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/clase_s1/datasets_powerbi_parcial/03_rendimiento_academico_powerbi.xlsx
+++ b/clase_s1/datasets_powerbi_parcial/03_rendimiento_academico_powerbi.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="1" r:id="R0b971098a3bf4c7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estudiantes" sheetId="2" r:id="R6e6a85b46a7a4480"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cursos" sheetId="3" r:id="Rd3e3032784c34101"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notas" sheetId="1" r:id="R4fa685785a844b4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estudiantes" sheetId="2" r:id="Re04682cbe2d940eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cursos" sheetId="3" r:id="Rcb90141bfde14926"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -76,15 +76,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NotasAcademicas" displayName="NotasAcademicas" ref="A1:G33" headerRowCount="1">
-  <x:tableColumns count="7">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NotasAcademicas" displayName="NotasAcademicas" ref="A1:H33" headerRowCount="1">
+  <x:tableColumns count="8">
     <x:tableColumn id="1" name="NotaID"/>
-    <x:tableColumn id="2" name="EstudianteID"/>
-    <x:tableColumn id="3" name="CursoID"/>
-    <x:tableColumn id="4" name="Evaluacion"/>
-    <x:tableColumn id="5" name="Nota"/>
-    <x:tableColumn id="6" name="AsistenciaPct"/>
-    <x:tableColumn id="7" name="EstadoEntrega"/>
+    <x:tableColumn id="2" name="FechaEvaluacion"/>
+    <x:tableColumn id="3" name="EstudianteID"/>
+    <x:tableColumn id="4" name="CursoID"/>
+    <x:tableColumn id="5" name="Evaluacion"/>
+    <x:tableColumn id="6" name="Nota"/>
+    <x:tableColumn id="7" name="AsistenciaPct"/>
+    <x:tableColumn id="8" name="EstadoEntrega"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -264,12 +265,13 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="11.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.5" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.5" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="11.880000114440918" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="17.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17.8799991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -277,21 +279,24 @@
         <x:v>NotaID</x:v>
       </x:c>
       <x:c r="B1" s="5" t="str">
+        <x:v>FechaEvaluacion</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="str">
         <x:v>EstudianteID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="D1" s="5" t="str">
         <x:v>CursoID</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="E1" s="5" t="str">
         <x:v>Evaluacion</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="F1" s="5" t="str">
         <x:v>Nota</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="G1" s="5" t="str">
         <x:v>AsistenciaPct</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="H1" s="5" t="str">
         <x:v>EstadoEntrega</x:v>
       </x:c>
     </x:row>
@@ -300,21 +305,24 @@
         <x:v>N11</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
+        <x:v>2025-02-05</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="C2" s="6" t="str">
+      <x:c r="D2" s="6" t="str">
         <x:v>CU01</x:v>
       </x:c>
-      <x:c r="D2" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="n">
+      <x:c r="E2" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="n">
         <x:v>2.4</x:v>
       </x:c>
-      <x:c r="F2" s="6" t="n">
+      <x:c r="G2" s="6" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G2" s="6" t="str">
+      <x:c r="H2" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -323,21 +331,24 @@
         <x:v>N12</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
+        <x:v>2025-03-09</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="C3" s="6" t="str">
+      <x:c r="D3" s="6" t="str">
         <x:v>CU02</x:v>
       </x:c>
-      <x:c r="D3" s="6" t="str">
+      <x:c r="E3" s="6" t="str">
         <x:v>Parcial 2</x:v>
       </x:c>
-      <x:c r="E3" s="6" t="n">
+      <x:c r="F3" s="6" t="n">
         <x:v>2.8</x:v>
       </x:c>
-      <x:c r="F3" s="6" t="n">
+      <x:c r="G3" s="6" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G3" s="6" t="str">
+      <x:c r="H3" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
@@ -346,21 +357,24 @@
         <x:v>N13</x:v>
       </x:c>
       <x:c r="B4" s="6" t="str">
+        <x:v>2025-04-13</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="C4" s="6" t="str">
+      <x:c r="D4" s="6" t="str">
         <x:v>CU03</x:v>
       </x:c>
-      <x:c r="D4" s="6" t="str">
+      <x:c r="E4" s="6" t="str">
         <x:v>Proyecto</x:v>
       </x:c>
-      <x:c r="E4" s="6" t="n">
+      <x:c r="F4" s="6" t="n">
         <x:v>3.2</x:v>
       </x:c>
-      <x:c r="F4" s="6" t="n">
+      <x:c r="G4" s="6" t="n">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="G4" s="6" t="str">
+      <x:c r="H4" s="6" t="str">
         <x:v>No entregado</x:v>
       </x:c>
     </x:row>
@@ -369,21 +383,24 @@
         <x:v>N14</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
+        <x:v>2025-05-17</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
         <x:v>E01</x:v>
       </x:c>
-      <x:c r="C5" s="6" t="str">
+      <x:c r="D5" s="6" t="str">
         <x:v>CU04</x:v>
       </x:c>
-      <x:c r="D5" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E5" s="6" t="n">
+      <x:c r="E5" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="n">
         <x:v>3.7</x:v>
       </x:c>
-      <x:c r="F5" s="6" t="n">
+      <x:c r="G5" s="6" t="n">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G5" s="6" t="str">
+      <x:c r="H5" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -392,21 +409,24 @@
         <x:v>N21</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
+        <x:v>2025-02-08</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="str">
+      <x:c r="D6" s="6" t="str">
         <x:v>CU01</x:v>
       </x:c>
-      <x:c r="D6" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="n">
+      <x:c r="E6" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="n">
         <x:v>2.7</x:v>
       </x:c>
-      <x:c r="F6" s="6" t="n">
+      <x:c r="G6" s="6" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G6" s="6" t="str">
+      <x:c r="H6" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
@@ -415,21 +435,24 @@
         <x:v>N22</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
+        <x:v>2025-03-12</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="D7" s="6" t="str">
         <x:v>CU02</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="E7" s="6" t="str">
         <x:v>Parcial 2</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="n">
+      <x:c r="F7" s="6" t="n">
         <x:v>3.1</x:v>
       </x:c>
-      <x:c r="F7" s="6" t="n">
+      <x:c r="G7" s="6" t="n">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G7" s="6" t="str">
+      <x:c r="H7" s="6" t="str">
         <x:v>No entregado</x:v>
       </x:c>
     </x:row>
@@ -438,21 +461,24 @@
         <x:v>N23</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
+        <x:v>2025-04-16</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="D8" s="6" t="str">
         <x:v>CU03</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="E8" s="6" t="str">
         <x:v>Proyecto</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="n">
+      <x:c r="F8" s="6" t="n">
         <x:v>3.6</x:v>
       </x:c>
-      <x:c r="F8" s="6" t="n">
+      <x:c r="G8" s="6" t="n">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="G8" s="6" t="str">
+      <x:c r="H8" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -461,21 +487,24 @@
         <x:v>N24</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
+        <x:v>2025-05-20</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
         <x:v>E02</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>CU04</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="n">
+      <x:c r="E9" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F9" s="6" t="n">
+      <x:c r="G9" s="6" t="n">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G9" s="6" t="str">
+      <x:c r="H9" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
@@ -484,21 +513,24 @@
         <x:v>N31</x:v>
       </x:c>
       <x:c r="B10" s="6" t="str">
+        <x:v>2025-02-11</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>CU01</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E10" s="6" t="n">
+      <x:c r="E10" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F10" s="6" t="n">
+      <x:c r="G10" s="6" t="n">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G10" s="6" t="str">
+      <x:c r="H10" s="6" t="str">
         <x:v>No entregado</x:v>
       </x:c>
     </x:row>
@@ -507,19 +539,22 @@
         <x:v>N32</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
+        <x:v>2025-03-15</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="C11" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>CU02</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
         <x:v>Parcial 2</x:v>
       </x:c>
-      <x:c r="E11" s="6"/>
-      <x:c r="F11" s="6" t="n">
+      <x:c r="F11" s="6"/>
+      <x:c r="G11" s="6" t="n">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G11" s="6" t="str">
+      <x:c r="H11" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -528,21 +563,24 @@
         <x:v>N33</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
+        <x:v>2025-04-19</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="D12" s="6" t="str">
         <x:v>CU03</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="E12" s="6" t="str">
         <x:v>Proyecto</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="n">
+      <x:c r="F12" s="6" t="n">
         <x:v>3.9</x:v>
       </x:c>
-      <x:c r="F12" s="6" t="n">
+      <x:c r="G12" s="6" t="n">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G12" s="6" t="str">
+      <x:c r="H12" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
@@ -551,21 +589,24 @@
         <x:v>N34</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
+        <x:v>2025-05-23</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
         <x:v>E03</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="str">
+      <x:c r="D13" s="6" t="str">
         <x:v>CU04</x:v>
       </x:c>
-      <x:c r="D13" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E13" s="6" t="n">
+      <x:c r="E13" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="n">
         <x:v>4.3</x:v>
       </x:c>
-      <x:c r="F13" s="6" t="n">
+      <x:c r="G13" s="6" t="n">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G13" s="6" t="str">
+      <x:c r="H13" s="6" t="str">
         <x:v>No entregado</x:v>
       </x:c>
     </x:row>
@@ -574,21 +615,24 @@
         <x:v>N41</x:v>
       </x:c>
       <x:c r="B14" s="6" t="str">
+        <x:v>2025-02-14</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="C14" s="6" t="str">
+      <x:c r="D14" s="6" t="str">
         <x:v>CU01</x:v>
       </x:c>
-      <x:c r="D14" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E14" s="6" t="n">
+      <x:c r="E14" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="n">
         <x:v>3.3</x:v>
       </x:c>
-      <x:c r="F14" s="6" t="n">
+      <x:c r="G14" s="6" t="n">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G14" s="6" t="str">
+      <x:c r="H14" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -597,21 +641,24 @@
         <x:v>N42</x:v>
       </x:c>
       <x:c r="B15" s="6" t="str">
+        <x:v>2025-03-18</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="C15" s="6" t="str">
+      <x:c r="D15" s="6" t="str">
         <x:v>CU02</x:v>
       </x:c>
-      <x:c r="D15" s="6" t="str">
+      <x:c r="E15" s="6" t="str">
         <x:v>Parcial 2</x:v>
       </x:c>
-      <x:c r="E15" s="6" t="n">
+      <x:c r="F15" s="6" t="n">
         <x:v>3.8</x:v>
       </x:c>
-      <x:c r="F15" s="6" t="n">
+      <x:c r="G15" s="6" t="n">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G15" s="6" t="str">
+      <x:c r="H15" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
@@ -620,21 +667,24 @@
         <x:v>N43</x:v>
       </x:c>
       <x:c r="B16" s="6" t="str">
+        <x:v>2025-04-22</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="C16" s="6" t="str">
+      <x:c r="D16" s="6" t="str">
         <x:v>CU03</x:v>
       </x:c>
-      <x:c r="D16" s="6" t="str">
+      <x:c r="E16" s="6" t="str">
         <x:v>Proyecto</x:v>
       </x:c>
-      <x:c r="E16" s="6" t="n">
+      <x:c r="F16" s="6" t="n">
         <x:v>4.2</x:v>
       </x:c>
-      <x:c r="F16" s="6" t="n">
+      <x:c r="G16" s="6" t="n">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G16" s="6" t="str">
+      <x:c r="H16" s="6" t="str">
         <x:v>No entregado</x:v>
       </x:c>
     </x:row>
@@ -643,21 +693,24 @@
         <x:v>N44</x:v>
       </x:c>
       <x:c r="B17" s="6" t="str">
+        <x:v>2025-05-06</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
         <x:v>E04</x:v>
       </x:c>
-      <x:c r="C17" s="6" t="str">
+      <x:c r="D17" s="6" t="str">
         <x:v>CU04</x:v>
       </x:c>
-      <x:c r="D17" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E17" s="6" t="n">
+      <x:c r="E17" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="F17" s="6" t="n">
+      <x:c r="G17" s="6" t="n">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G17" s="6" t="str">
+      <x:c r="H17" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -666,21 +719,24 @@
         <x:v>N51</x:v>
       </x:c>
       <x:c r="B18" s="6" t="str">
+        <x:v>2025-02-17</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="C18" s="6" t="str">
+      <x:c r="D18" s="6" t="str">
         <x:v>CU01</x:v>
       </x:c>
-      <x:c r="D18" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E18" s="6" t="n">
+      <x:c r="E18" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F18" s="6" t="n">
         <x:v>3.6</x:v>
       </x:c>
-      <x:c r="F18" s="6" t="n">
+      <x:c r="G18" s="6" t="n">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G18" s="6" t="str">
+      <x:c r="H18" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
@@ -689,21 +745,24 @@
         <x:v>N52</x:v>
       </x:c>
       <x:c r="B19" s="6" t="str">
+        <x:v>2025-03-21</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="C19" s="6" t="str">
+      <x:c r="D19" s="6" t="str">
         <x:v>CU02</x:v>
       </x:c>
-      <x:c r="D19" s="6" t="str">
+      <x:c r="E19" s="6" t="str">
         <x:v>Parcial 2</x:v>
       </x:c>
-      <x:c r="E19" s="6" t="n">
+      <x:c r="F19" s="6" t="n">
         <x:v>4.1</x:v>
       </x:c>
-      <x:c r="F19" s="6" t="n">
+      <x:c r="G19" s="6" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G19" s="6" t="str">
+      <x:c r="H19" s="6" t="str">
         <x:v>No entregado</x:v>
       </x:c>
     </x:row>
@@ -712,21 +771,24 @@
         <x:v>N53</x:v>
       </x:c>
       <x:c r="B20" s="6" t="str">
+        <x:v>2025-04-05</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="C20" s="6" t="str">
+      <x:c r="D20" s="6" t="str">
         <x:v>CU03</x:v>
       </x:c>
-      <x:c r="D20" s="6" t="str">
+      <x:c r="E20" s="6" t="str">
         <x:v>Proyecto</x:v>
       </x:c>
-      <x:c r="E20" s="6" t="n">
+      <x:c r="F20" s="6" t="n">
         <x:v>4.5</x:v>
       </x:c>
-      <x:c r="F20" s="6" t="n">
+      <x:c r="G20" s="6" t="n">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="G20" s="6" t="str">
+      <x:c r="H20" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -735,21 +797,24 @@
         <x:v>N54</x:v>
       </x:c>
       <x:c r="B21" s="6" t="str">
+        <x:v>2025-05-09</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
         <x:v>E05</x:v>
       </x:c>
-      <x:c r="C21" s="6" t="str">
+      <x:c r="D21" s="6" t="str">
         <x:v>CU04</x:v>
       </x:c>
-      <x:c r="D21" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E21" s="6" t="n">
+      <x:c r="E21" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F21" s="6" t="n">
         <x:v>4.9</x:v>
       </x:c>
-      <x:c r="F21" s="6" t="n">
+      <x:c r="G21" s="6" t="n">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G21" s="6" t="str">
+      <x:c r="H21" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
@@ -758,21 +823,24 @@
         <x:v>N61</x:v>
       </x:c>
       <x:c r="B22" s="6" t="str">
+        <x:v>2025-02-20</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="C22" s="6" t="str">
+      <x:c r="D22" s="6" t="str">
         <x:v>CU01</x:v>
       </x:c>
-      <x:c r="D22" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E22" s="6" t="n">
+      <x:c r="E22" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F22" s="6" t="n">
+      <x:c r="G22" s="6" t="n">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G22" s="6" t="str">
+      <x:c r="H22" s="6" t="str">
         <x:v>No entregado</x:v>
       </x:c>
     </x:row>
@@ -781,21 +849,24 @@
         <x:v>N62</x:v>
       </x:c>
       <x:c r="B23" s="6" t="str">
+        <x:v>2025-03-24</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="C23" s="6" t="str">
+      <x:c r="D23" s="6" t="str">
         <x:v>CU02</x:v>
       </x:c>
-      <x:c r="D23" s="6" t="str">
+      <x:c r="E23" s="6" t="str">
         <x:v>Parcial 2</x:v>
       </x:c>
-      <x:c r="E23" s="6" t="n">
+      <x:c r="F23" s="6" t="n">
         <x:v>4.4</x:v>
       </x:c>
-      <x:c r="F23" s="6" t="n">
+      <x:c r="G23" s="6" t="n">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G23" s="6" t="str">
+      <x:c r="H23" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -804,21 +875,24 @@
         <x:v>N63</x:v>
       </x:c>
       <x:c r="B24" s="6" t="str">
+        <x:v>2025-04-08</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="C24" s="6" t="str">
+      <x:c r="D24" s="6" t="str">
         <x:v>CU03</x:v>
       </x:c>
-      <x:c r="D24" s="6" t="str">
+      <x:c r="E24" s="6" t="str">
         <x:v>Proyecto</x:v>
       </x:c>
-      <x:c r="E24" s="6" t="n">
+      <x:c r="F24" s="6" t="n">
         <x:v>4.8</x:v>
       </x:c>
-      <x:c r="F24" s="6" t="n">
+      <x:c r="G24" s="6" t="n">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="G24" s="6" t="str">
+      <x:c r="H24" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
@@ -827,21 +901,24 @@
         <x:v>N64</x:v>
       </x:c>
       <x:c r="B25" s="6" t="str">
+        <x:v>2025-05-12</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
         <x:v>E06</x:v>
       </x:c>
-      <x:c r="C25" s="6" t="str">
+      <x:c r="D25" s="6" t="str">
         <x:v>CU04</x:v>
       </x:c>
-      <x:c r="D25" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E25" s="6" t="n">
+      <x:c r="E25" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F25" s="6" t="n">
         <x:v>2.6</x:v>
       </x:c>
-      <x:c r="F25" s="6" t="n">
+      <x:c r="G25" s="6" t="n">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="G25" s="6" t="str">
+      <x:c r="H25" s="6" t="str">
         <x:v>No entregado</x:v>
       </x:c>
     </x:row>
@@ -850,21 +927,24 @@
         <x:v>N71</x:v>
       </x:c>
       <x:c r="B26" s="6" t="str">
+        <x:v>2025-02-23</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="C26" s="6" t="str">
+      <x:c r="D26" s="6" t="str">
         <x:v>CU01</x:v>
       </x:c>
-      <x:c r="D26" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E26" s="6" t="n">
+      <x:c r="E26" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="n">
         <x:v>4.3</x:v>
       </x:c>
-      <x:c r="F26" s="6" t="n">
+      <x:c r="G26" s="6" t="n">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="G26" s="6" t="str">
+      <x:c r="H26" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -873,21 +953,24 @@
         <x:v>N72</x:v>
       </x:c>
       <x:c r="B27" s="6" t="str">
+        <x:v>2025-03-07</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="C27" s="6" t="str">
+      <x:c r="D27" s="6" t="str">
         <x:v>CU02</x:v>
       </x:c>
-      <x:c r="D27" s="6" t="str">
+      <x:c r="E27" s="6" t="str">
         <x:v>Parcial 2</x:v>
       </x:c>
-      <x:c r="E27" s="6" t="n">
+      <x:c r="F27" s="6" t="n">
         <x:v>4.7</x:v>
       </x:c>
-      <x:c r="F27" s="6" t="n">
+      <x:c r="G27" s="6" t="n">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G27" s="6" t="str">
+      <x:c r="H27" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
@@ -896,21 +979,24 @@
         <x:v>N73</x:v>
       </x:c>
       <x:c r="B28" s="6" t="str">
+        <x:v>2025-04-11</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="C28" s="6" t="str">
+      <x:c r="D28" s="6" t="str">
         <x:v>CU03</x:v>
       </x:c>
-      <x:c r="D28" s="6" t="str">
+      <x:c r="E28" s="6" t="str">
         <x:v>Proyecto</x:v>
       </x:c>
-      <x:c r="E28" s="6" t="n">
+      <x:c r="F28" s="6" t="n">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="F28" s="6" t="n">
+      <x:c r="G28" s="6" t="n">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="G28" s="6" t="str">
+      <x:c r="H28" s="6" t="str">
         <x:v>No entregado</x:v>
       </x:c>
     </x:row>
@@ -919,21 +1005,24 @@
         <x:v>N74</x:v>
       </x:c>
       <x:c r="B29" s="6" t="str">
+        <x:v>2025-05-15</x:v>
+      </x:c>
+      <x:c r="C29" s="6" t="str">
         <x:v>E07</x:v>
       </x:c>
-      <x:c r="C29" s="6" t="str">
+      <x:c r="D29" s="6" t="str">
         <x:v>CU04</x:v>
       </x:c>
-      <x:c r="D29" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E29" s="6" t="n">
+      <x:c r="E29" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F29" s="6" t="n">
         <x:v>2.9</x:v>
       </x:c>
-      <x:c r="F29" s="6" t="n">
+      <x:c r="G29" s="6" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G29" s="6" t="str">
+      <x:c r="H29" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -942,21 +1031,24 @@
         <x:v>N81</x:v>
       </x:c>
       <x:c r="B30" s="6" t="str">
+        <x:v>2025-02-06</x:v>
+      </x:c>
+      <x:c r="C30" s="6" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="C30" s="6" t="str">
+      <x:c r="D30" s="6" t="str">
         <x:v>CU01</x:v>
       </x:c>
-      <x:c r="D30" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E30" s="6" t="n">
+      <x:c r="E30" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F30" s="6" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="F30" s="6" t="n">
+      <x:c r="G30" s="6" t="n">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="G30" s="6" t="str">
+      <x:c r="H30" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
@@ -965,21 +1057,24 @@
         <x:v>N82</x:v>
       </x:c>
       <x:c r="B31" s="6" t="str">
+        <x:v>2025-03-10</x:v>
+      </x:c>
+      <x:c r="C31" s="6" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="C31" s="6" t="str">
+      <x:c r="D31" s="6" t="str">
         <x:v>CU02</x:v>
       </x:c>
-      <x:c r="D31" s="6" t="str">
+      <x:c r="E31" s="6" t="str">
         <x:v>Parcial 2</x:v>
       </x:c>
-      <x:c r="E31" s="6" t="n">
+      <x:c r="F31" s="6" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F31" s="6" t="n">
+      <x:c r="G31" s="6" t="n">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="G31" s="6" t="str">
+      <x:c r="H31" s="6" t="str">
         <x:v>No entregado</x:v>
       </x:c>
     </x:row>
@@ -988,21 +1083,24 @@
         <x:v>N83</x:v>
       </x:c>
       <x:c r="B32" s="6" t="str">
+        <x:v>2025-04-14</x:v>
+      </x:c>
+      <x:c r="C32" s="6" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="C32" s="6" t="str">
+      <x:c r="D32" s="6" t="str">
         <x:v>CU03</x:v>
       </x:c>
-      <x:c r="D32" s="6" t="str">
+      <x:c r="E32" s="6" t="str">
         <x:v>Proyecto</x:v>
       </x:c>
-      <x:c r="E32" s="6" t="n">
+      <x:c r="F32" s="6" t="n">
         <x:v>2.8</x:v>
       </x:c>
-      <x:c r="F32" s="6" t="n">
+      <x:c r="G32" s="6" t="n">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="G32" s="6" t="str">
+      <x:c r="H32" s="6" t="str">
         <x:v>Entregado</x:v>
       </x:c>
     </x:row>
@@ -1011,28 +1109,31 @@
         <x:v>N84</x:v>
       </x:c>
       <x:c r="B33" s="6" t="str">
+        <x:v>2025-05-18</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="str">
         <x:v>E08</x:v>
       </x:c>
-      <x:c r="C33" s="6" t="str">
+      <x:c r="D33" s="6" t="str">
         <x:v>CU04</x:v>
       </x:c>
-      <x:c r="D33" s="6" t="str">
-        <x:v>Parcial 1</x:v>
-      </x:c>
-      <x:c r="E33" s="6" t="n">
+      <x:c r="E33" s="6" t="str">
+        <x:v>Parcial 1</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="n">
         <x:v>3.2</x:v>
       </x:c>
-      <x:c r="F33" s="6" t="n">
+      <x:c r="G33" s="6" t="n">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G33" s="6" t="str">
+      <x:c r="H33" s="6" t="str">
         <x:v>Tarde</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04ad3ee2af184d40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45ff16bccd14f94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1176,7 +1277,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a04afce7fc34940"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00d34e52fb8c4887"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1264,7 +1365,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac6190e54a56457f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd273c44c320343cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>